--- a/analysis_results/calibration_rebuild_20260702/worker_facing_distribution_release_v3_1/任务分发表.xlsx
+++ b/analysis_results/calibration_rebuild_20260702/worker_facing_distribution_release_v3_1/任务分发表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\HOHONET\analysis_results\calibration_rebuild_20260702\worker_facing_distribution_release_v3_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7BE71-49C4-45AD-A15E-727DBF453DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87AF7DA-4086-440B-8C63-407BA207C6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1548" yWindow="1656" windowWidth="23040" windowHeight="12120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1548" yWindow="1656" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="112">
   <si>
     <t>说明</t>
   </si>
@@ -362,11 +362,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请按 task_code 找任务，例如 任务1-001、任务2-017、任务3-002。</t>
+    <t>任务1/2/3 是三个不同入口；同一个编号在不同入口不是同一个任务。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>任务1/2/3 是三个不同入口；同一个编号在不同入口不是同一个任务。</t>
+    <t>task_code</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请按 task_code 找任务，"-"后面的是每个project的内部顺序(inner_id)。例如 任务1-001、任务2-017、任务3-002。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -386,6 +390,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -753,12 +758,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1879,13 +1884,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
